--- a/Telephone Directory-2026.xlsx
+++ b/Telephone Directory-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ujjwalmahajan/Desktop/UJJWAL_LAB/NIPER/MANAGEMENT/Telephone_Directory/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A367F7-1E15-B943-87A7-DA31F82955F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD85AF96-771E-1445-8C9C-56772BD38A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-32960" yWindow="-7380" windowWidth="30240" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -588,10 +588,6 @@
     <t xml:space="preserve"> Mr. Uma</t>
   </si>
   <si>
-    <t>Prof. Anupama Mittal
- Prof. Incharge</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Mr. Shantaram R.Bhade /  Ms. Beena /  Mr. Gagandeep Singh</t>
   </si>
   <si>
@@ -793,6 +789,9 @@
   </si>
   <si>
     <t>Dr. Shyam Sunder Sharma</t>
+  </si>
+  <si>
+    <t>Prof. Anupama Mittal</t>
   </si>
 </sst>
 </file>
@@ -1165,12 +1164,12 @@
         <v>106</v>
       </c>
       <c r="D1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B2">
         <v>2204</v>
@@ -1179,23 +1178,23 @@
         <v>2148</v>
       </c>
       <c r="D2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B3">
         <v>2215</v>
       </c>
       <c r="D3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>187</v>
+        <v>253</v>
       </c>
       <c r="B4">
         <v>2007</v>
@@ -1206,10 +1205,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D5" t="s">
         <v>0</v>
@@ -1228,7 +1227,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B7">
         <v>2074</v>
@@ -1245,18 +1244,18 @@
         <v>2022</v>
       </c>
       <c r="D8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B9">
         <v>2265</v>
       </c>
       <c r="D9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1267,7 +1266,7 @@
         <v>2023</v>
       </c>
       <c r="D10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -1278,7 +1277,7 @@
         <v>2026</v>
       </c>
       <c r="D11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -1289,7 +1288,7 @@
         <v>2187</v>
       </c>
       <c r="D12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -1300,7 +1299,7 @@
         <v>2045</v>
       </c>
       <c r="D13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -1311,7 +1310,7 @@
         <v>2030</v>
       </c>
       <c r="D14" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -1322,18 +1321,18 @@
         <v>2029</v>
       </c>
       <c r="D15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B16">
         <v>2228</v>
       </c>
       <c r="D16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -1341,7 +1340,7 @@
         <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -1352,7 +1351,7 @@
         <v>2036</v>
       </c>
       <c r="D18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -1363,7 +1362,7 @@
         <v>2035</v>
       </c>
       <c r="D19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -1374,7 +1373,7 @@
         <v>2171</v>
       </c>
       <c r="D20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -1385,7 +1384,7 @@
         <v>2262</v>
       </c>
       <c r="D21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -1396,7 +1395,7 @@
         <v>2084</v>
       </c>
       <c r="D22" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -1407,7 +1406,7 @@
         <v>2042</v>
       </c>
       <c r="D23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -1418,7 +1417,7 @@
         <v>2041</v>
       </c>
       <c r="D24" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -1429,7 +1428,7 @@
         <v>2048</v>
       </c>
       <c r="D25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -1440,7 +1439,7 @@
         <v>2218</v>
       </c>
       <c r="D26" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -1451,18 +1450,18 @@
         <v>2054</v>
       </c>
       <c r="D27" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B28">
         <v>2123</v>
       </c>
       <c r="D28" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -1473,7 +1472,7 @@
         <v>2052</v>
       </c>
       <c r="D29" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -1484,18 +1483,18 @@
         <v>2058</v>
       </c>
       <c r="D30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B31">
         <v>2188</v>
       </c>
       <c r="D31" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -1506,7 +1505,7 @@
         <v>2169</v>
       </c>
       <c r="D32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -1517,7 +1516,7 @@
         <v>2170</v>
       </c>
       <c r="D33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -1528,7 +1527,7 @@
         <v>2062</v>
       </c>
       <c r="D34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -1539,7 +1538,7 @@
         <v>2064</v>
       </c>
       <c r="D35" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -1550,7 +1549,7 @@
         <v>2136</v>
       </c>
       <c r="D36" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -1561,7 +1560,7 @@
         <v>2167</v>
       </c>
       <c r="D37" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -1572,7 +1571,7 @@
         <v>2032</v>
       </c>
       <c r="D38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -1580,7 +1579,7 @@
         <v>94</v>
       </c>
       <c r="D39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -1591,7 +1590,7 @@
         <v>2130</v>
       </c>
       <c r="D40" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -1602,7 +1601,7 @@
         <v>2059</v>
       </c>
       <c r="D41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -1613,7 +1612,7 @@
         <v>2124</v>
       </c>
       <c r="D42" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -1624,7 +1623,7 @@
         <v>2050</v>
       </c>
       <c r="D43" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -1635,7 +1634,7 @@
         <v>2127</v>
       </c>
       <c r="D44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -1646,7 +1645,7 @@
         <v>2247</v>
       </c>
       <c r="D45" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -1657,7 +1656,7 @@
         <v>2038</v>
       </c>
       <c r="D46" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -1668,7 +1667,7 @@
         <v>2141</v>
       </c>
       <c r="D47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -1679,7 +1678,7 @@
         <v>2269</v>
       </c>
       <c r="D48" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -1690,7 +1689,7 @@
         <v>2015</v>
       </c>
       <c r="D49" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -1701,7 +1700,7 @@
         <v>2019</v>
       </c>
       <c r="D50" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -1712,40 +1711,40 @@
         <v>2013</v>
       </c>
       <c r="D51" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B52">
         <v>2046</v>
       </c>
       <c r="D52" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B53">
         <v>2017</v>
       </c>
       <c r="D53" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B54">
         <v>2174</v>
       </c>
       <c r="D54" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -1761,7 +1760,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B56">
         <v>2216</v>
@@ -1772,7 +1771,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B57">
         <v>2235</v>
@@ -1783,7 +1782,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B58">
         <v>2149</v>
@@ -1794,7 +1793,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B59">
         <v>2197</v>
@@ -1827,7 +1826,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B62">
         <v>2078</v>
@@ -2003,38 +2002,38 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B78" t="s">
         <v>22</v>
       </c>
       <c r="D78" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B79" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C79" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D79" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B80">
         <v>2006</v>
       </c>
       <c r="D80" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
@@ -2072,7 +2071,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B84">
         <v>2223</v>
@@ -2083,7 +2082,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B85">
         <v>2009</v>
@@ -2092,7 +2091,7 @@
         <v>2020</v>
       </c>
       <c r="D85" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
@@ -2111,7 +2110,7 @@
         <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D87" t="s">
         <v>25</v>
@@ -2171,7 +2170,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B93" t="s">
         <v>34</v>
@@ -2182,7 +2181,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B94" t="s">
         <v>35</v>
@@ -2235,7 +2234,7 @@
         <v>2168</v>
       </c>
       <c r="D98" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
@@ -2249,7 +2248,7 @@
         <v>2213</v>
       </c>
       <c r="D99" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
@@ -2260,7 +2259,7 @@
         <v>2280</v>
       </c>
       <c r="D100" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
@@ -2274,7 +2273,7 @@
         <v>2092</v>
       </c>
       <c r="D101" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
@@ -2288,7 +2287,7 @@
         <v>2101</v>
       </c>
       <c r="D102" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
@@ -2302,7 +2301,7 @@
         <v>2117</v>
       </c>
       <c r="D103" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
@@ -2316,7 +2315,7 @@
         <v>2093</v>
       </c>
       <c r="D104" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
@@ -2330,7 +2329,7 @@
         <v>2108</v>
       </c>
       <c r="D105" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
@@ -2341,7 +2340,7 @@
         <v>2217</v>
       </c>
       <c r="D106" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
@@ -2352,7 +2351,7 @@
         <v>2033</v>
       </c>
       <c r="D107" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
@@ -2363,7 +2362,7 @@
         <v>2063</v>
       </c>
       <c r="D108" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
@@ -2374,7 +2373,7 @@
         <v>2278</v>
       </c>
       <c r="D109" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
@@ -2385,7 +2384,7 @@
         <v>2289</v>
       </c>
       <c r="D110" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
@@ -2396,7 +2395,7 @@
         <v>2257</v>
       </c>
       <c r="D111" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
@@ -2410,7 +2409,7 @@
         <v>2103</v>
       </c>
       <c r="D112" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
@@ -2424,7 +2423,7 @@
         <v>2113</v>
       </c>
       <c r="D113" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
@@ -2438,7 +2437,7 @@
         <v>108</v>
       </c>
       <c r="D114" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
@@ -2452,7 +2451,7 @@
         <v>2160</v>
       </c>
       <c r="D115" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
@@ -2463,7 +2462,7 @@
         <v>2027</v>
       </c>
       <c r="D116" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
@@ -2474,7 +2473,7 @@
         <v>2125</v>
       </c>
       <c r="D117" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
@@ -2485,7 +2484,7 @@
         <v>2049</v>
       </c>
       <c r="D118" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
@@ -2496,7 +2495,7 @@
         <v>2287</v>
       </c>
       <c r="D119" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
@@ -2510,7 +2509,7 @@
         <v>2100</v>
       </c>
       <c r="D120" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
@@ -2524,7 +2523,7 @@
         <v>2236</v>
       </c>
       <c r="D121" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
@@ -2535,7 +2534,7 @@
         <v>2291</v>
       </c>
       <c r="D122" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
@@ -2546,7 +2545,7 @@
         <v>2284</v>
       </c>
       <c r="D123" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
@@ -2560,7 +2559,7 @@
         <v>2116</v>
       </c>
       <c r="D124" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
@@ -2571,7 +2570,7 @@
         <v>2158</v>
       </c>
       <c r="D125" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
@@ -2582,7 +2581,7 @@
         <v>2016</v>
       </c>
       <c r="D126" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
@@ -2596,7 +2595,7 @@
         <v>2111</v>
       </c>
       <c r="D127" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
@@ -2607,7 +2606,7 @@
         <v>2227</v>
       </c>
       <c r="D128" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
@@ -2621,7 +2620,7 @@
         <v>2104</v>
       </c>
       <c r="D129" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
@@ -2632,7 +2631,7 @@
         <v>2288</v>
       </c>
       <c r="D130" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
@@ -2643,7 +2642,7 @@
         <v>2283</v>
       </c>
       <c r="D131" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
@@ -2654,7 +2653,7 @@
         <v>2281</v>
       </c>
       <c r="D132" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
@@ -2668,12 +2667,12 @@
         <v>2173</v>
       </c>
       <c r="D133" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B134">
         <v>2040</v>
@@ -2682,7 +2681,7 @@
         <v>2106</v>
       </c>
       <c r="D134" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
@@ -2696,7 +2695,7 @@
         <v>2109</v>
       </c>
       <c r="D135" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
@@ -2707,7 +2706,7 @@
         <v>2290</v>
       </c>
       <c r="D136" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
@@ -2721,7 +2720,7 @@
         <v>2047</v>
       </c>
       <c r="D137" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
@@ -2732,7 +2731,7 @@
         <v>2286</v>
       </c>
       <c r="D138" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
@@ -2743,7 +2742,7 @@
         <v>2031</v>
       </c>
       <c r="D139" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
@@ -2754,7 +2753,7 @@
         <v>2285</v>
       </c>
       <c r="D140" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
@@ -2768,7 +2767,7 @@
         <v>2209</v>
       </c>
       <c r="D141" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
@@ -2779,7 +2778,7 @@
         <v>2279</v>
       </c>
       <c r="D142" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
@@ -2790,7 +2789,7 @@
         <v>2266</v>
       </c>
       <c r="D143" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
@@ -2872,7 +2871,7 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B151">
         <v>2009</v>
@@ -2894,7 +2893,7 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B153">
         <v>2099</v>
@@ -2938,7 +2937,7 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B157">
         <v>2192</v>
@@ -2960,7 +2959,7 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B159">
         <v>2222</v>
@@ -2969,7 +2968,7 @@
         <v>2114</v>
       </c>
       <c r="D159" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
@@ -3040,7 +3039,7 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B166">
         <v>2219</v>
@@ -3078,35 +3077,35 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B170">
         <v>2004</v>
       </c>
       <c r="D170" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B171" t="s">
         <v>21</v>
       </c>
       <c r="D171" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B172">
         <v>2008</v>
       </c>
       <c r="D172" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
@@ -3147,18 +3146,18 @@
         <v>139</v>
       </c>
       <c r="B176" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C176" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D176" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B177">
         <v>2086</v>
@@ -3378,7 +3377,7 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B197">
         <v>2089</v>
@@ -3389,7 +3388,7 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B198">
         <v>2090</v>
@@ -3400,7 +3399,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B199">
         <v>2238</v>
@@ -3411,7 +3410,7 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B200">
         <v>2185</v>
@@ -3466,7 +3465,7 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B205" t="s">
         <v>113</v>

--- a/Telephone Directory-2026.xlsx
+++ b/Telephone Directory-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ujjwalmahajan/Desktop/UJJWAL_LAB/NIPER/MANAGEMENT/Telephone_Directory/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD85AF96-771E-1445-8C9C-56772BD38A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66576D4-F105-114D-84D3-E525B36FAEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-32960" yWindow="-7380" windowWidth="30240" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1149,8 +1149,10 @@
   <dimension ref="A1:D205"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="46.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="59.1640625" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="4" max="4" width="41.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">

--- a/Telephone Directory-2026.xlsx
+++ b/Telephone Directory-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10415"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ujjwalmahajan/Desktop/UJJWAL_LAB/NIPER/MANAGEMENT/Telephone_Directory/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66576D4-F105-114D-84D3-E525B36FAEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5746EEA2-3A9E-0649-89EC-167D8AE0A8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32960" yWindow="-7380" windowWidth="30240" windowHeight="17780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="253">
   <si>
     <t>ACADEMICS &amp; EXAMINATION</t>
   </si>
@@ -66,9 +66,6 @@
     <t xml:space="preserve"> Medical Emergency Vehicle</t>
   </si>
   <si>
-    <t xml:space="preserve"> NIPER Crèche</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Swimming Pool</t>
   </si>
   <si>
@@ -108,21 +105,9 @@
     <t>Consultant Engineering</t>
   </si>
   <si>
-    <t xml:space="preserve">  Engg Dept. (Office)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Er. Major Singh </t>
-  </si>
-  <si>
     <t>Er. T.P. Singh</t>
   </si>
   <si>
-    <t xml:space="preserve">  Mr. Kamal Kishore</t>
-  </si>
-  <si>
     <t>ESTABLISHMENT SECTION</t>
   </si>
   <si>
@@ -186,9 +171,6 @@
     <t xml:space="preserve"> First Floor</t>
   </si>
   <si>
-    <t xml:space="preserve"> Mr. Anurag  Sharma</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Committee Room</t>
   </si>
   <si>
@@ -225,63 +207,9 @@
     <t>TECHNOLOGY DEVELOPMENT CENTRE</t>
   </si>
   <si>
-    <t xml:space="preserve">  Plant (Ground Floor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Utility Room (Ground Floor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  TDC (First Floor)</t>
-  </si>
-  <si>
     <t>STAFF RESIDENCE</t>
   </si>
   <si>
-    <t xml:space="preserve">  Type-II House No.1-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Type-III House No.1-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Type-III House No.7-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Type-III House No.13-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Type-III House No.19-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Type-III House No.31-36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Type-IV House No.1-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Type-IV House No.7-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Mr. Vikas Grover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Mr. Vinod Kumar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Ground Floor Corridor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Office (Ms.Yogita)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Ground Floor (Corridor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Second Floor (Corridor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Office </t>
-  </si>
-  <si>
     <t>NATURAL PRODUCTS</t>
   </si>
   <si>
@@ -312,9 +240,6 @@
     <t>PHARMACY PRACTICE</t>
   </si>
   <si>
-    <t xml:space="preserve"> Office (Ms Meena)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Mr. Baljinder Singh</t>
   </si>
   <si>
@@ -336,12 +261,6 @@
     <t xml:space="preserve"> Main Gate</t>
   </si>
   <si>
-    <t xml:space="preserve">  Security Post (Near TDC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Security Post (DT Resi.)</t>
-  </si>
-  <si>
     <t>FACULTY</t>
   </si>
   <si>
@@ -375,9 +294,6 @@
     <t>2245 / 2088</t>
   </si>
   <si>
-    <t xml:space="preserve"> Ms. Kanwaljit K. /                Mr. Inderjit S.</t>
-  </si>
-  <si>
     <t>CENTRE FOR INFECTIOUS DISEASES</t>
   </si>
   <si>
@@ -390,9 +306,6 @@
     <t xml:space="preserve"> Mr. Arun Gautam / Mr.Sunil Pandey</t>
   </si>
   <si>
-    <t xml:space="preserve"> Mr. Jairaj Meena       </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Legal Cell (Mr. Deepraj Sharma)</t>
   </si>
   <si>
@@ -405,9 +318,6 @@
     <t xml:space="preserve">Ms. Sukhwinder </t>
   </si>
   <si>
-    <t xml:space="preserve"> Mr. Ashu Kumar / Mr.  Anil Bhardwaj</t>
-  </si>
-  <si>
     <t>DISPENSARY</t>
   </si>
   <si>
@@ -432,27 +342,12 @@
     <t>STUDENTS HOSTELS</t>
   </si>
   <si>
-    <t xml:space="preserve">  First Floor (Corridor) Dr. Mennakshi / Mr. Ravi P Reddy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Room No. B-310 (Dr. Raj Kumar Mishra)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Security post                                (P-1; Back Gate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Security post    (Teaching    &amp;  Research Blocks)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wg Cdr PJP Singh Waraich (Retd.) </t>
   </si>
   <si>
     <t>Dr. Sandeep Dinday</t>
   </si>
   <si>
-    <t>Telephone Exchange                    (Mr. Kuldip Chouhan)</t>
-  </si>
-  <si>
     <t>9 / 2292000 /2214688</t>
   </si>
   <si>
@@ -540,9 +435,6 @@
     <t>Dr. Abhay T. Sangamwar</t>
   </si>
   <si>
-    <t xml:space="preserve">  Process Control Lab.         (First Floor)</t>
-  </si>
-  <si>
     <t>Dr. Pravin Keshaorao Shinde</t>
   </si>
   <si>
@@ -579,16 +471,10 @@
     <t>Dr. Deepak B. Salunke</t>
   </si>
   <si>
-    <t>Hostel Warden (Office)                   Mr. Baldev Raj</t>
-  </si>
-  <si>
     <t>Dr. Pooja Arora</t>
   </si>
   <si>
     <t xml:space="preserve"> Mr. Uma</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mr. Shantaram R.Bhade /  Ms. Beena /  Mr. Gagandeep Singh</t>
   </si>
   <si>
     <t>Reception</t>
@@ -625,21 +511,6 @@
 (Mr. Lipton Sharma)</t>
   </si>
   <si>
-    <t xml:space="preserve">  SUTLEJ (Old Boys’ Hostel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  BEAS (New Boys’ Hostel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  CHENAB (Boys’ Hostel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  RAAVI (Girls’ Hostel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Dosage Plant (Mr. Raj Kumar Banoth)</t>
-  </si>
-  <si>
     <t>2001 / 2214690</t>
   </si>
   <si>
@@ -673,9 +544,6 @@
     <t>Director</t>
   </si>
   <si>
-    <t xml:space="preserve"> Prof. Dulal Panda</t>
-  </si>
-  <si>
     <t>PA to Director</t>
   </si>
   <si>
@@ -694,9 +562,6 @@
     <t>PA to Registrar</t>
   </si>
   <si>
-    <t xml:space="preserve">  Ms. Meenakshi</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Registrar's Office</t>
   </si>
   <si>
@@ -733,31 +598,12 @@
     <t>BLOCK – H &amp; Block –I PHARM.TECH. (PTF/PTPC/PTBT)</t>
   </si>
   <si>
-    <t xml:space="preserve">  Security Supervisor              (Mr. Devender Kumar)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Ms. Prakriti Aggarwal SO (Exam.)</t>
   </si>
   <si>
-    <t xml:space="preserve">  Mr. Sanjay Kumar Room No. C-303</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mr. Gunjan Kohli                       Room No.E-111</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mr. Rahul Mahajan                   Room No.E-115</t>
-  </si>
-  <si>
     <t>Dr. Pooja Arora Room No.A-308</t>
   </si>
   <si>
-    <t xml:space="preserve">  Prof. K.B. Tikoo Dean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Mr. Naresh Kumar 
-</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Mr. Manoj Tiwari AR (Estt.)</t>
   </si>
   <si>
@@ -767,21 +613,9 @@
     <t xml:space="preserve"> Sh. Jitender K. Chandel DR(F&amp;A)</t>
   </si>
   <si>
-    <t xml:space="preserve"> QA Office Ms. Kanwaljit K ./               Dr. Malti S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Mr Lalit Sood </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Mr. Manoj Sood </t>
-  </si>
-  <si>
     <t>Ms. Usha</t>
   </si>
   <si>
-    <t xml:space="preserve"> Dr. Shrikant Bhagat</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Corridor COMPUTER CENTRE</t>
   </si>
   <si>
@@ -792,6 +626,168 @@
   </si>
   <si>
     <t>Prof. Anupama Mittal</t>
+  </si>
+  <si>
+    <t>Ground Floor (Corridor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Gunjan Kohli Room No.E-111</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Rahul Mahajan Room No.E-115</t>
+  </si>
+  <si>
+    <t>Hostel Warden (Office) Mr. Baldev Raj</t>
+  </si>
+  <si>
+    <t>Office (Ms.Yogita)</t>
+  </si>
+  <si>
+    <t>Dr. Shrikant Bhagat</t>
+  </si>
+  <si>
+    <t>Second Floor (Corridor)</t>
+  </si>
+  <si>
+    <t>First Floor (Corridor) Dr. Mennakshi / Mr. Ravi P Reddy</t>
+  </si>
+  <si>
+    <t>Room No. B-310 (Dr. Raj Kumar Mishra)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office </t>
+  </si>
+  <si>
+    <t>Office (Ms Meena)</t>
+  </si>
+  <si>
+    <t>NIPER Crèche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Naresh Kumar </t>
+  </si>
+  <si>
+    <t>Prof. K.B. Tikoo Dean</t>
+  </si>
+  <si>
+    <t>Prof. Dulal Panda</t>
+  </si>
+  <si>
+    <t>SUTLEJ (Old Boys’ Hostel)</t>
+  </si>
+  <si>
+    <t>BEAS (New Boys’ Hostel)</t>
+  </si>
+  <si>
+    <t>CHENAB (Boys’ Hostel)</t>
+  </si>
+  <si>
+    <t>RAAVI (Girls’ Hostel)</t>
+  </si>
+  <si>
+    <t>Plant (Ground Floor)</t>
+  </si>
+  <si>
+    <t>Utility Room (Ground Floor)</t>
+  </si>
+  <si>
+    <t>Process Control Lab. (First Floor)</t>
+  </si>
+  <si>
+    <t>TDC (First Floor)</t>
+  </si>
+  <si>
+    <t>Dosage Plant (Mr. Raj Kumar Banoth)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Shantaram R.Bhade /Ms. Beena /Mr. Gagandeep Singh</t>
+  </si>
+  <si>
+    <t>Mr. Sanjay Kumar Room No. C-303</t>
+  </si>
+  <si>
+    <t>Mr. Vikas Grover</t>
+  </si>
+  <si>
+    <t>Mr. Vinod Kumar</t>
+  </si>
+  <si>
+    <t>Ground Floor Corridor</t>
+  </si>
+  <si>
+    <t>Telephone Exchange(Mr. Kuldip Chouhan)</t>
+  </si>
+  <si>
+    <t>Engg Dept. (Office)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Er. Major Singh </t>
+  </si>
+  <si>
+    <t>Mr. Kamal Kishore</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Ashu Kumar / Mr.Anil Bhardwaj</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. AnuragSharma</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ms. Kanwaljit K. /Mr. Inderjit S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> QA Office Ms. Kanwaljit K ./ Dr. Malti S</t>
+  </si>
+  <si>
+    <t>Ms. Meenakshi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr Lalit Sood </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Manoj Sood </t>
+  </si>
+  <si>
+    <t>Security Supervisor(Mr. Devender Kumar)</t>
+  </si>
+  <si>
+    <t>Security post(Teaching&amp;Research Blocks)</t>
+  </si>
+  <si>
+    <t>Security post(P-1; Back Gate)</t>
+  </si>
+  <si>
+    <t>Security Post (Near TDC)</t>
+  </si>
+  <si>
+    <t>Security Post (DT Resi.)</t>
+  </si>
+  <si>
+    <t>Type-II House No.1-12</t>
+  </si>
+  <si>
+    <t>Type-III House No.1-6</t>
+  </si>
+  <si>
+    <t>Type-III House No.7-12</t>
+  </si>
+  <si>
+    <t>Type-III House No.13-18</t>
+  </si>
+  <si>
+    <t>Type-III House No.19-24</t>
+  </si>
+  <si>
+    <t>Type-III House No.31-36</t>
+  </si>
+  <si>
+    <t>Type-IV House No.1-6</t>
+  </si>
+  <si>
+    <t>Type-IV House No.7-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mr. Jairaj Meena </t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D8B77F-ED62-3C42-AE92-B987220EEA50}">
-  <dimension ref="A1:D205"/>
+  <dimension ref="A1:D203"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="59.1640625" customWidth="1"/>
@@ -1157,21 +1153,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="D1" t="s">
-        <v>205</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="B2">
         <v>2204</v>
@@ -1180,23 +1176,23 @@
         <v>2148</v>
       </c>
       <c r="D2" t="s">
-        <v>209</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="B3">
         <v>2215</v>
       </c>
       <c r="D3" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>253</v>
+        <v>198</v>
       </c>
       <c r="B4">
         <v>2007</v>
@@ -1207,10 +1203,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>235</v>
+        <v>189</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="D5" t="s">
         <v>0</v>
@@ -1218,7 +1214,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="B6">
         <v>2200</v>
@@ -1229,7 +1225,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="B7">
         <v>2074</v>
@@ -1240,521 +1236,524 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="B8">
         <v>2022</v>
       </c>
       <c r="D8" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>249</v>
+        <v>204</v>
       </c>
       <c r="B9">
         <v>2265</v>
       </c>
       <c r="D9" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="B10">
         <v>2023</v>
       </c>
       <c r="D10" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="B11">
         <v>2026</v>
       </c>
       <c r="D11" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="B12">
         <v>2187</v>
       </c>
       <c r="D12" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="B13">
         <v>2045</v>
       </c>
       <c r="D13" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="B14">
         <v>2030</v>
       </c>
       <c r="D14" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="B15">
         <v>2029</v>
       </c>
       <c r="D15" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="B16">
         <v>2228</v>
       </c>
       <c r="D16" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B18">
         <v>2036</v>
       </c>
       <c r="D18" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="B19">
         <v>2035</v>
       </c>
       <c r="D19" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B20">
         <v>2171</v>
       </c>
       <c r="D20" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="B21">
         <v>2262</v>
       </c>
       <c r="D21" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="B22">
         <v>2084</v>
       </c>
       <c r="D22" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B23">
         <v>2042</v>
       </c>
       <c r="D23" t="s">
-        <v>229</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="B24">
         <v>2041</v>
       </c>
       <c r="D24" t="s">
-        <v>229</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="B25">
         <v>2048</v>
       </c>
       <c r="D25" t="s">
-        <v>229</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B26">
         <v>2218</v>
       </c>
       <c r="D26" t="s">
-        <v>229</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B27">
         <v>2054</v>
       </c>
       <c r="D27" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="B28">
         <v>2123</v>
       </c>
       <c r="D28" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="B29">
         <v>2052</v>
       </c>
       <c r="D29" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="B30">
         <v>2058</v>
       </c>
       <c r="D30" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="B31">
         <v>2188</v>
       </c>
       <c r="D31" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="B32">
         <v>2169</v>
       </c>
       <c r="D32" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B33">
         <v>2170</v>
       </c>
       <c r="D33" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B34">
         <v>2062</v>
       </c>
       <c r="D34" t="s">
-        <v>231</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="B35">
         <v>2064</v>
       </c>
       <c r="D35" t="s">
-        <v>231</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="B36">
         <v>2136</v>
       </c>
       <c r="D36" t="s">
-        <v>231</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="B37">
         <v>2167</v>
       </c>
       <c r="D37" t="s">
-        <v>231</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B38">
         <v>2032</v>
       </c>
       <c r="D38" t="s">
-        <v>232</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>94</v>
+        <v>209</v>
+      </c>
+      <c r="B39">
+        <v>2130</v>
       </c>
       <c r="D39" t="s">
-        <v>232</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B40">
-        <v>2130</v>
+        <v>2059</v>
       </c>
       <c r="D40" t="s">
-        <v>232</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="B41">
-        <v>2059</v>
+        <v>2124</v>
       </c>
       <c r="D41" t="s">
-        <v>232</v>
+        <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="B42">
-        <v>2124</v>
+        <v>2050</v>
       </c>
       <c r="D42" t="s">
-        <v>233</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="B43">
-        <v>2050</v>
+        <v>2127</v>
       </c>
       <c r="D43" t="s">
-        <v>233</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B44">
-        <v>2127</v>
+        <v>2247</v>
       </c>
       <c r="D44" t="s">
-        <v>233</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="B45">
-        <v>2247</v>
+        <v>2038</v>
       </c>
       <c r="D45" t="s">
-        <v>233</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="B46">
-        <v>2038</v>
+        <v>2141</v>
       </c>
       <c r="D46" t="s">
-        <v>233</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B47">
-        <v>2141</v>
+        <v>2269</v>
       </c>
       <c r="D47" t="s">
-        <v>233</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>225</v>
       </c>
       <c r="B48">
-        <v>2269</v>
+        <v>2015</v>
       </c>
       <c r="D48" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="B49">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D49" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="B50">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="D50" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="B51">
-        <v>2013</v>
+        <v>2046</v>
       </c>
       <c r="D51" t="s">
-        <v>225</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="B52">
-        <v>2046</v>
+        <v>2017</v>
       </c>
       <c r="D52" t="s">
-        <v>226</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
       <c r="B53">
-        <v>2017</v>
+        <v>2174</v>
       </c>
       <c r="D53" t="s">
-        <v>226</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="B54">
-        <v>2174</v>
+        <v>2201</v>
       </c>
       <c r="D54" t="s">
-        <v>226</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>2</v>
+        <v>152</v>
       </c>
       <c r="B55">
-        <v>2201</v>
+        <v>2216</v>
       </c>
       <c r="D55" t="s">
         <v>1</v>
@@ -1762,10 +1761,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="B56">
-        <v>2216</v>
+        <v>2235</v>
       </c>
       <c r="D56" t="s">
         <v>1</v>
@@ -1773,10 +1772,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="B57">
-        <v>2235</v>
+        <v>2149</v>
       </c>
       <c r="D57" t="s">
         <v>1</v>
@@ -1784,10 +1783,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B58">
-        <v>2149</v>
+        <v>2197</v>
       </c>
       <c r="D58" t="s">
         <v>1</v>
@@ -1795,10 +1794,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>197</v>
+        <v>3</v>
       </c>
       <c r="B59">
-        <v>2197</v>
+        <v>2191</v>
       </c>
       <c r="D59" t="s">
         <v>1</v>
@@ -1806,10 +1805,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="B60">
-        <v>2191</v>
+        <v>2277</v>
       </c>
       <c r="D60" t="s">
         <v>1</v>
@@ -1817,21 +1816,21 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="B61">
-        <v>2277</v>
+        <v>2078</v>
       </c>
       <c r="D61" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>223</v>
+        <v>6</v>
       </c>
       <c r="B62">
-        <v>2078</v>
+        <v>2143</v>
       </c>
       <c r="D62" t="s">
         <v>5</v>
@@ -1839,10 +1838,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B63">
-        <v>2143</v>
+        <v>2203</v>
       </c>
       <c r="D63" t="s">
         <v>5</v>
@@ -1850,21 +1849,21 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B64">
-        <v>2203</v>
+        <v>2077</v>
       </c>
       <c r="D64" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>9</v>
-      </c>
-      <c r="B65">
-        <v>2077</v>
+        <v>10</v>
+      </c>
+      <c r="B65" t="s">
+        <v>23</v>
       </c>
       <c r="D65" t="s">
         <v>8</v>
@@ -1872,10 +1871,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>10</v>
+        <v>228</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="D66" t="s">
         <v>8</v>
@@ -1883,10 +1882,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>141</v>
-      </c>
-      <c r="B67" t="s">
-        <v>142</v>
+        <v>11</v>
+      </c>
+      <c r="B67">
+        <v>2075</v>
       </c>
       <c r="D67" t="s">
         <v>8</v>
@@ -1894,10 +1893,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="B68">
-        <v>2075</v>
+        <v>2270</v>
       </c>
       <c r="D68" t="s">
         <v>8</v>
@@ -1905,10 +1904,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="B69">
-        <v>2270</v>
+        <v>2246</v>
       </c>
       <c r="D69" t="s">
         <v>8</v>
@@ -1919,7 +1918,7 @@
         <v>13</v>
       </c>
       <c r="B70">
-        <v>2246</v>
+        <v>2225</v>
       </c>
       <c r="D70" t="s">
         <v>8</v>
@@ -1930,7 +1929,7 @@
         <v>14</v>
       </c>
       <c r="B71">
-        <v>2225</v>
+        <v>2248</v>
       </c>
       <c r="D71" t="s">
         <v>8</v>
@@ -1941,7 +1940,7 @@
         <v>15</v>
       </c>
       <c r="B72">
-        <v>2248</v>
+        <v>2076</v>
       </c>
       <c r="D72" t="s">
         <v>8</v>
@@ -1949,13 +1948,13 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73">
+        <v>2070</v>
+      </c>
+      <c r="D73" t="s">
         <v>16</v>
-      </c>
-      <c r="B73">
-        <v>2076</v>
-      </c>
-      <c r="D73" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
@@ -1963,1066 +1962,1063 @@
         <v>18</v>
       </c>
       <c r="B74">
-        <v>2070</v>
+        <v>2080</v>
       </c>
       <c r="D74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B75">
-        <v>2080</v>
+        <v>2217</v>
       </c>
       <c r="D75" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B76">
-        <v>2217</v>
+        <v>2242</v>
       </c>
       <c r="D76" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>4</v>
-      </c>
-      <c r="B77">
-        <v>2242</v>
+        <v>212</v>
+      </c>
+      <c r="B77" t="s">
+        <v>21</v>
       </c>
       <c r="D77" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="B78" t="s">
-        <v>22</v>
+        <v>160</v>
+      </c>
+      <c r="C78" t="s">
+        <v>158</v>
       </c>
       <c r="D78" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>214</v>
-      </c>
-      <c r="B79" t="s">
-        <v>203</v>
-      </c>
-      <c r="C79" t="s">
-        <v>196</v>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B79">
+        <v>2006</v>
       </c>
       <c r="D79" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A80" s="1" t="s">
-        <v>241</v>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>98</v>
       </c>
       <c r="B80">
-        <v>2006</v>
+        <v>2118</v>
       </c>
       <c r="D80" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="B81">
-        <v>2118</v>
+        <v>2146</v>
       </c>
       <c r="D81" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>129</v>
+        <v>12</v>
       </c>
       <c r="B82">
-        <v>2146</v>
+        <v>2270</v>
       </c>
       <c r="D82" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="B83">
-        <v>2270</v>
+        <v>2223</v>
       </c>
       <c r="D83" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="B84">
-        <v>2223</v>
+        <v>2009</v>
+      </c>
+      <c r="C84">
+        <v>2020</v>
       </c>
       <c r="D84" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>210</v>
+        <v>25</v>
       </c>
       <c r="B85">
-        <v>2009</v>
-      </c>
-      <c r="C85">
-        <v>2020</v>
+        <v>2271</v>
       </c>
       <c r="D85" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>26</v>
-      </c>
-      <c r="B86">
-        <v>2271</v>
+        <v>229</v>
+      </c>
+      <c r="B86" t="s">
+        <v>179</v>
       </c>
       <c r="D86" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>27</v>
-      </c>
-      <c r="B87" t="s">
-        <v>224</v>
-      </c>
       <c r="D87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>28</v>
+        <v>230</v>
+      </c>
+      <c r="B88">
+        <v>2056</v>
       </c>
       <c r="D88" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B89">
-        <v>2056</v>
+        <v>2082</v>
       </c>
       <c r="D89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>30</v>
+        <v>231</v>
       </c>
       <c r="B90">
-        <v>2082</v>
+        <v>2254</v>
       </c>
       <c r="D90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B91">
-        <v>2254</v>
+        <v>2221</v>
       </c>
       <c r="D91" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>33</v>
-      </c>
-      <c r="B92">
-        <v>2221</v>
+        <v>191</v>
+      </c>
+      <c r="B92" t="s">
+        <v>29</v>
       </c>
       <c r="D92" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>242</v>
+        <v>192</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D93" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>243</v>
-      </c>
-      <c r="B94" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="B94">
+        <v>2053</v>
       </c>
       <c r="D94" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="B95">
-        <v>2053</v>
+        <v>2161</v>
       </c>
       <c r="D95" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>125</v>
+        <v>232</v>
       </c>
       <c r="B96">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="D96" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="B97">
-        <v>2162</v>
+        <v>2068</v>
+      </c>
+      <c r="C97">
+        <v>2168</v>
       </c>
       <c r="D97" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B98">
-        <v>2068</v>
+        <v>2211</v>
       </c>
       <c r="C98">
-        <v>2168</v>
+        <v>2213</v>
       </c>
       <c r="D98" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="B99">
-        <v>2211</v>
-      </c>
-      <c r="C99">
-        <v>2213</v>
+        <v>2280</v>
       </c>
       <c r="D99" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B100">
-        <v>2280</v>
+        <v>2096</v>
+      </c>
+      <c r="C100">
+        <v>2092</v>
       </c>
       <c r="D100" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="B101">
-        <v>2096</v>
+        <v>2157</v>
       </c>
       <c r="C101">
-        <v>2092</v>
+        <v>2101</v>
       </c>
       <c r="D101" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="B102">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="C102">
-        <v>2101</v>
+        <v>2117</v>
       </c>
       <c r="D102" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="B103">
-        <v>2159</v>
+        <v>2282</v>
       </c>
       <c r="C103">
-        <v>2117</v>
+        <v>2093</v>
       </c>
       <c r="D103" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="B104">
-        <v>2282</v>
+        <v>2126</v>
       </c>
       <c r="C104">
-        <v>2093</v>
+        <v>2108</v>
       </c>
       <c r="D104" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="B105">
-        <v>2126</v>
-      </c>
-      <c r="C105">
-        <v>2108</v>
+        <v>2217</v>
       </c>
       <c r="D105" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B106">
-        <v>2217</v>
+        <v>2033</v>
       </c>
       <c r="D106" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="B107">
-        <v>2033</v>
+        <v>2063</v>
       </c>
       <c r="D107" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B108">
-        <v>2063</v>
+        <v>2278</v>
       </c>
       <c r="D108" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>183</v>
+        <v>144</v>
       </c>
       <c r="B109">
-        <v>2278</v>
+        <v>2289</v>
       </c>
       <c r="D109" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="B110">
-        <v>2289</v>
+        <v>2257</v>
       </c>
       <c r="D110" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B111">
-        <v>2257</v>
+        <v>2065</v>
+      </c>
+      <c r="C111">
+        <v>2103</v>
       </c>
       <c r="D111" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="B112">
-        <v>2065</v>
+        <v>2152</v>
       </c>
       <c r="C112">
-        <v>2103</v>
+        <v>2113</v>
       </c>
       <c r="D112" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="B113">
-        <v>2152</v>
-      </c>
-      <c r="C113">
-        <v>2113</v>
+        <v>2144</v>
+      </c>
+      <c r="C113" t="s">
+        <v>81</v>
       </c>
       <c r="D113" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="B114">
-        <v>2144</v>
-      </c>
-      <c r="C114" t="s">
-        <v>108</v>
+        <v>2061</v>
+      </c>
+      <c r="C114">
+        <v>2160</v>
       </c>
       <c r="D114" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="B115">
-        <v>2061</v>
-      </c>
-      <c r="C115">
-        <v>2160</v>
+        <v>2027</v>
       </c>
       <c r="D115" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B116">
-        <v>2027</v>
+        <v>2125</v>
       </c>
       <c r="D116" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="B117">
-        <v>2125</v>
+        <v>2049</v>
       </c>
       <c r="D117" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="B118">
-        <v>2049</v>
+        <v>2287</v>
       </c>
       <c r="D118" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="B119">
-        <v>2287</v>
+        <v>2025</v>
+      </c>
+      <c r="C119">
+        <v>2100</v>
       </c>
       <c r="D119" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="B120">
-        <v>2025</v>
+        <v>2147</v>
       </c>
       <c r="C120">
-        <v>2100</v>
+        <v>2236</v>
       </c>
       <c r="D120" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="B121">
-        <v>2147</v>
-      </c>
-      <c r="C121">
-        <v>2236</v>
+        <v>2291</v>
       </c>
       <c r="D121" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="B122">
-        <v>2291</v>
+        <v>2284</v>
       </c>
       <c r="D122" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="B123">
-        <v>2284</v>
+        <v>2018</v>
+      </c>
+      <c r="C123">
+        <v>2116</v>
       </c>
       <c r="D123" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B124">
-        <v>2018</v>
-      </c>
-      <c r="C124">
-        <v>2116</v>
+        <v>2158</v>
       </c>
       <c r="D124" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="B125">
-        <v>2158</v>
+        <v>2016</v>
       </c>
       <c r="D125" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="B126">
-        <v>2016</v>
+        <v>2135</v>
+      </c>
+      <c r="C126">
+        <v>2111</v>
       </c>
       <c r="D126" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="B127">
-        <v>2135</v>
-      </c>
-      <c r="C127">
-        <v>2111</v>
+        <v>2227</v>
       </c>
       <c r="D127" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>172</v>
+        <v>128</v>
       </c>
       <c r="B128">
-        <v>2227</v>
+        <v>2024</v>
+      </c>
+      <c r="C128">
+        <v>2104</v>
       </c>
       <c r="D128" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="B129">
-        <v>2024</v>
-      </c>
-      <c r="C129">
-        <v>2104</v>
+        <v>2288</v>
       </c>
       <c r="D129" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="B130">
-        <v>2288</v>
+        <v>2283</v>
       </c>
       <c r="D130" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="B131">
-        <v>2283</v>
+        <v>2281</v>
       </c>
       <c r="D131" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="B132">
-        <v>2281</v>
+        <v>2172</v>
+      </c>
+      <c r="C132">
+        <v>2173</v>
       </c>
       <c r="D132" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="B133">
-        <v>2172</v>
+        <v>2040</v>
       </c>
       <c r="C133">
-        <v>2173</v>
+        <v>2106</v>
       </c>
       <c r="D133" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>252</v>
+        <v>130</v>
       </c>
       <c r="B134">
-        <v>2040</v>
+        <v>2037</v>
       </c>
       <c r="C134">
-        <v>2106</v>
+        <v>2109</v>
       </c>
       <c r="D134" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="B135">
-        <v>2037</v>
-      </c>
-      <c r="C135">
-        <v>2109</v>
+        <v>2290</v>
       </c>
       <c r="D135" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="B136">
-        <v>2290</v>
+        <v>2055</v>
+      </c>
+      <c r="C136">
+        <v>2047</v>
       </c>
       <c r="D136" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="B137">
-        <v>2055</v>
-      </c>
-      <c r="C137">
-        <v>2047</v>
+        <v>2286</v>
       </c>
       <c r="D137" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>182</v>
+        <v>133</v>
       </c>
       <c r="B138">
-        <v>2286</v>
+        <v>2031</v>
       </c>
       <c r="D138" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="B139">
-        <v>2031</v>
+        <v>2285</v>
       </c>
       <c r="D139" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="B140">
-        <v>2285</v>
+        <v>2208</v>
+      </c>
+      <c r="C140">
+        <v>2209</v>
       </c>
       <c r="D140" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>169</v>
+        <v>108</v>
       </c>
       <c r="B141">
-        <v>2208</v>
-      </c>
-      <c r="C141">
-        <v>2209</v>
+        <v>2279</v>
       </c>
       <c r="D141" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="B142">
-        <v>2279</v>
+        <v>2266</v>
       </c>
       <c r="D142" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>111</v>
-      </c>
-      <c r="B143">
-        <v>2266</v>
+        <v>33</v>
+      </c>
+      <c r="B143" t="s">
+        <v>88</v>
       </c>
       <c r="D143" t="s">
-        <v>206</v>
+        <v>32</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>38</v>
-      </c>
-      <c r="B144" t="s">
-        <v>115</v>
+        <v>34</v>
+      </c>
+      <c r="B144">
+        <v>2181</v>
       </c>
       <c r="D144" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>39</v>
-      </c>
-      <c r="B145">
-        <v>2181</v>
+        <v>35</v>
+      </c>
+      <c r="B145" t="s">
+        <v>87</v>
       </c>
       <c r="D145" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>40</v>
-      </c>
-      <c r="B146" t="s">
-        <v>114</v>
+        <v>36</v>
+      </c>
+      <c r="B146">
+        <v>2182</v>
       </c>
       <c r="D146" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B147">
-        <v>2182</v>
+        <v>2179</v>
       </c>
       <c r="D147" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B148">
-        <v>2179</v>
+        <v>2183</v>
       </c>
       <c r="D148" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B149">
-        <v>2183</v>
+        <v>2180</v>
       </c>
       <c r="D149" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
       <c r="B150">
-        <v>2180</v>
+        <v>2009</v>
       </c>
       <c r="D150" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>244</v>
+        <v>94</v>
       </c>
       <c r="B151">
-        <v>2009</v>
+        <v>2034</v>
       </c>
       <c r="D151" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="B152">
-        <v>2034</v>
+        <v>2099</v>
       </c>
       <c r="D152" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>192</v>
+        <v>41</v>
       </c>
       <c r="B153">
-        <v>2099</v>
+        <v>2268</v>
       </c>
       <c r="D153" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B154">
-        <v>2268</v>
+        <v>2196</v>
       </c>
       <c r="D154" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B155">
-        <v>2196</v>
+        <v>2249</v>
       </c>
       <c r="D155" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="B156">
-        <v>2249</v>
+        <v>2192</v>
       </c>
       <c r="D156" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="B157">
-        <v>2192</v>
+        <v>2251</v>
       </c>
       <c r="D157" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="B158">
-        <v>2251</v>
+        <v>2222</v>
+      </c>
+      <c r="C158">
+        <v>2114</v>
       </c>
       <c r="D158" t="s">
-        <v>45</v>
+        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>211</v>
+        <v>45</v>
       </c>
       <c r="B159">
-        <v>2222</v>
-      </c>
-      <c r="C159">
-        <v>2114</v>
+        <v>2073</v>
       </c>
       <c r="D159" t="s">
-        <v>208</v>
+        <v>44</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B160">
-        <v>2073</v>
+        <v>2210</v>
       </c>
       <c r="D160" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B161">
-        <v>2210</v>
+        <v>2069</v>
       </c>
       <c r="D161" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>52</v>
+        <v>233</v>
       </c>
       <c r="B162">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="D162" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B163">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="D163" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>54</v>
-      </c>
-      <c r="B164">
-        <v>2072</v>
+        <v>234</v>
+      </c>
+      <c r="B164" t="s">
+        <v>50</v>
       </c>
       <c r="D164" t="s">
         <v>49</v>
@@ -3030,455 +3026,439 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>116</v>
-      </c>
-      <c r="B165" t="s">
-        <v>56</v>
+        <v>235</v>
+      </c>
+      <c r="B165">
+        <v>2219</v>
       </c>
       <c r="D165" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>245</v>
-      </c>
-      <c r="B166">
-        <v>2219</v>
+        <v>102</v>
+      </c>
+      <c r="B166" t="s">
+        <v>52</v>
       </c>
       <c r="D166" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>132</v>
-      </c>
-      <c r="B167" t="s">
-        <v>58</v>
+        <v>4</v>
+      </c>
+      <c r="B167">
+        <v>2084</v>
       </c>
       <c r="D167" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>236</v>
+      </c>
+      <c r="B168">
+        <v>2004</v>
+      </c>
       <c r="D168" t="s">
-        <v>57</v>
+        <v>174</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>4</v>
-      </c>
-      <c r="B169">
-        <v>2084</v>
+        <v>237</v>
+      </c>
+      <c r="B169" t="s">
+        <v>20</v>
       </c>
       <c r="D169" t="s">
-        <v>59</v>
+        <v>171</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B170">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="D170" t="s">
-        <v>218</v>
+        <v>176</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>246</v>
-      </c>
-      <c r="B171" t="s">
-        <v>21</v>
+        <v>55</v>
+      </c>
+      <c r="B171">
+        <v>2163</v>
       </c>
       <c r="D171" t="s">
-        <v>215</v>
+        <v>54</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>247</v>
+        <v>56</v>
       </c>
       <c r="B172">
-        <v>2008</v>
+        <v>2165</v>
       </c>
       <c r="D172" t="s">
-        <v>220</v>
+        <v>54</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="B173">
-        <v>2163</v>
+        <v>2156</v>
       </c>
       <c r="D173" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>62</v>
-      </c>
-      <c r="B174">
-        <v>2165</v>
+        <v>105</v>
+      </c>
+      <c r="B174" t="s">
+        <v>157</v>
+      </c>
+      <c r="C174" t="s">
+        <v>156</v>
       </c>
       <c r="D174" t="s">
-        <v>60</v>
+        <v>175</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>4</v>
+        <v>239</v>
       </c>
       <c r="B175">
-        <v>2156</v>
+        <v>2086</v>
       </c>
       <c r="D175" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>139</v>
-      </c>
-      <c r="B176" t="s">
-        <v>195</v>
-      </c>
-      <c r="C176" t="s">
-        <v>194</v>
+        <v>77</v>
+      </c>
+      <c r="B176">
+        <v>2085</v>
       </c>
       <c r="D176" t="s">
-        <v>219</v>
+        <v>76</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B177">
-        <v>2086</v>
+        <v>2012</v>
       </c>
       <c r="D177" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>102</v>
+        <v>241</v>
       </c>
       <c r="B178">
-        <v>2085</v>
+        <v>2154</v>
       </c>
       <c r="D178" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="B179">
-        <v>2012</v>
+        <v>2155</v>
       </c>
       <c r="D179" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="B180">
-        <v>2154</v>
+        <v>2230</v>
       </c>
       <c r="D180" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>103</v>
+        <v>244</v>
       </c>
       <c r="B181">
-        <v>2155</v>
+        <v>2240</v>
       </c>
       <c r="D181" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>104</v>
+        <v>245</v>
       </c>
       <c r="B182">
-        <v>2230</v>
+        <v>2131</v>
       </c>
       <c r="D182" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>70</v>
+        <v>246</v>
       </c>
       <c r="B183">
-        <v>2240</v>
+        <v>2194</v>
       </c>
       <c r="D183" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>71</v>
+        <v>247</v>
       </c>
       <c r="B184">
-        <v>2131</v>
+        <v>2128</v>
       </c>
       <c r="D184" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>72</v>
+        <v>248</v>
       </c>
       <c r="B185">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="D185" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>73</v>
+        <v>249</v>
       </c>
       <c r="B186">
-        <v>2128</v>
+        <v>2232</v>
       </c>
       <c r="D186" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>74</v>
+        <v>250</v>
       </c>
       <c r="B187">
-        <v>2193</v>
+        <v>2132</v>
       </c>
       <c r="D187" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>75</v>
+        <v>251</v>
       </c>
       <c r="B188">
-        <v>2232</v>
+        <v>2184</v>
       </c>
       <c r="D188" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="B189">
-        <v>2132</v>
+        <v>2229</v>
       </c>
       <c r="D189" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="B190">
-        <v>2184</v>
+        <v>2010</v>
       </c>
       <c r="D190" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>118</v>
+        <v>252</v>
       </c>
       <c r="B191">
-        <v>2229</v>
+        <v>2134</v>
       </c>
       <c r="D191" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="B192">
-        <v>2010</v>
+        <v>2207</v>
       </c>
       <c r="D192" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="B193">
-        <v>2134</v>
+        <v>2129</v>
       </c>
       <c r="D193" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="B194">
-        <v>2207</v>
+        <v>2239</v>
       </c>
       <c r="D194" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>64</v>
+        <v>214</v>
       </c>
       <c r="B195">
-        <v>2129</v>
+        <v>2089</v>
       </c>
       <c r="D195" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="B196">
-        <v>2239</v>
+        <v>2090</v>
       </c>
       <c r="D196" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B197">
-        <v>2089</v>
+        <v>2238</v>
       </c>
       <c r="D197" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B198">
-        <v>2090</v>
+        <v>2185</v>
       </c>
       <c r="D198" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>200</v>
-      </c>
-      <c r="B199">
-        <v>2238</v>
+        <v>218</v>
+      </c>
+      <c r="B199" t="s">
+        <v>85</v>
       </c>
       <c r="D199" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="B200">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="D200" t="s">
-        <v>134</v>
+        <v>59</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>66</v>
-      </c>
-      <c r="B201" t="s">
-        <v>112</v>
+        <v>220</v>
+      </c>
+      <c r="B201">
+        <v>2189</v>
       </c>
       <c r="D201" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>67</v>
+        <v>221</v>
       </c>
       <c r="B202">
-        <v>2186</v>
+        <v>2151</v>
       </c>
       <c r="D202" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>171</v>
-      </c>
-      <c r="B203">
-        <v>2189</v>
+        <v>222</v>
+      </c>
+      <c r="B203" t="s">
+        <v>86</v>
       </c>
       <c r="D203" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A204" t="s">
-        <v>68</v>
-      </c>
-      <c r="B204">
-        <v>2151</v>
-      </c>
-      <c r="D204" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A205" t="s">
-        <v>202</v>
-      </c>
-      <c r="B205" t="s">
-        <v>113</v>
-      </c>
-      <c r="D205" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D250">
-    <sortCondition ref="D2:D250"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D248">
+    <sortCondition ref="D2:D248"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
